--- a/DOSSIES_MULTIFORMATO/SETRAB/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SETRAB/dossie.xlsx
@@ -628,7 +628,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2016NE00612</t>
+          <t>2016NE00614</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.55</v>
+        <v>563.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2016NE00614</t>
+          <t>2016NE00612</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>563.4</v>
+        <v>26.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -706,21 +706,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2016NE00571</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+          <t>2016NE00564</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>30/11/2016</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>193.3</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -762,17 +758,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2016NE00564</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>2016NE00571</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>30/11/2016</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>193.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2019NE00104</t>
+          <t>2019NE00105</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>981.58</v>
+        <v>5440</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2019NE00106</t>
+          <t>2019NE00109</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>981.58</v>
+        <v>1815.33</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2019NE00108</t>
+          <t>2019NE00102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2019NE00112</t>
+          <t>2019NE00107</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>981.58</v>
+        <v>1815.33</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2019NE00107</t>
+          <t>2019NE00112</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1815.33</v>
+        <v>981.58</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2019NE00102</t>
+          <t>2019NE00108</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -998,7 +998,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2019NE00109</t>
+          <t>2019NE00106</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1815.33</v>
+        <v>981.58</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2019NE00105</t>
+          <t>2019NE00104</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5440</v>
+        <v>981.58</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2017NE00406</t>
+          <t>2017NE00405</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>94.81</v>
+        <v>26.55</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1077,14 +1077,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anulação da NE n.058/2017 Motivo: Em atenção ao Encerramento do Exercício de 2017 - Instrução Normativa n.0001/2017.</t>
+          <t>Anulação da NE n.024/2017 Motivo: Em atenção ao Encerramento do Exercício de 2017 - Instrução Normativa n.0001/2017.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2017NE00405</t>
+          <t>2017NE00406</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>26.55</v>
+        <v>94.81</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1103,14 +1103,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anulação da NE n.024/2017 Motivo: Em atenção ao Encerramento do Exercício de 2017 - Instrução Normativa n.0001/2017.</t>
+          <t>Anulação da NE n.058/2017 Motivo: Em atenção ao Encerramento do Exercício de 2017 - Instrução Normativa n.0001/2017.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2019NE00101</t>
+          <t>2019NE00111</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1815.33</v>
+        <v>5440</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2019NE00111</t>
+          <t>2019NE00101</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5440</v>
+        <v>1815.33</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2018NE00584</t>
+          <t>2018NE00576</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>66101.46000000001</v>
+        <v>1689.62</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1219,14 +1219,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>ANULAÇÃO QUE SE FAZ DO SALDO DE EMPENHO EM ATENDIMENTO IN Nº 01/2018-SET-SEFAZ DE 30/11/2018 (ENCERRAMENTO DO EXERCÍCIO 2018)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2018NE00568</t>
+          <t>2018NE00580</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4217.15</v>
+        <v>847.45</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ANULAÇÃO QUE SE FAZ DO SALDO DE EMPENHO EM ATENDIMENTO IN Nº 01/2018-SET-SEFAZ DE 30/11/2018 (ENCERRAMENTO DO EXERCÍCIO 2018)</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2018NE00580</t>
+          <t>2018NE00568</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>847.45</v>
+        <v>4217.15</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1271,14 +1271,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>ANULAÇÃO QUE SE FAZ DO SALDO DE EMPENHO EM ATENDIMENTO IN Nº 01/2018-SET-SEFAZ DE 30/11/2018 (ENCERRAMENTO DO EXERCÍCIO 2018)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2018NE00576</t>
+          <t>2018NE00584</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1689.62</v>
+        <v>66101.46000000001</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ANULAÇÃO QUE SE FAZ DO SALDO DE EMPENHO EM ATENDIMENTO IN Nº 01/2018-SET-SEFAZ DE 30/11/2018 (ENCERRAMENTO DO EXERCÍCIO 2018)</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2019NE00490</t>
+          <t>2019NE00476</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1815.33</v>
+        <v>2780</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2019NE00492</t>
+          <t>2019NE00516</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1815.33</v>
+        <v>3401.58</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2019NE00488</t>
+          <t>2019NE00567</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>981.58</v>
+        <v>2780</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1461,14 +1461,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2019NE00486</t>
+          <t>2019NE00557</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>362.67</v>
+        <v>5440</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1487,14 +1487,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00046 e 2019GR00064</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2019NE00473</t>
+          <t>2019NE00472</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1815.33</v>
+        <v>981.58</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2019NE00481</t>
+          <t>2019NE00479</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1694.31</v>
+        <v>165.78</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2019NE00495</t>
+          <t>2019NE00470</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2780</v>
+        <v>5440</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2019NE00482</t>
+          <t>2019NE00544</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2594.67</v>
+        <v>2780</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1591,28 +1591,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO 542 EQUIVOCO NA MODALIDADE DE LICITAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2019NE00533</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00556</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>981.58</v>
+        <v>2780</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,14 +1617,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00048, 2019GR00049</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00045 e 2019GR00063.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2019NE00534</t>
+          <t>2019NE00530</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1642,7 +1638,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>981.58</v>
+        <v>1815.33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1651,14 +1647,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão. 2019GR00082 e 2019GR00083.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00051 E 2019GR00071</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2019NE00471</t>
+          <t>2019NE00469</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1668,7 +1664,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5440</v>
+        <v>2780</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1684,7 +1680,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2019NE00491</t>
+          <t>2019NE00565</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1694,7 +1690,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2780</v>
+        <v>185.33</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1703,14 +1699,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2019NE00568</t>
+          <t>2019NE00480</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1720,7 +1716,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1694.31</v>
+        <v>5077.33</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1729,14 +1725,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão, Competência: Julho/18.</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2019NE00563</t>
+          <t>2019NE00485</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1755,24 +1751,28 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão.</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2019NE00564</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>2019NE00540</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>362.67</v>
+        <v>1815.33</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1781,14 +1781,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2019NE00560</t>
+          <t>2019NE00562</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2594.67</v>
+        <v>121.02</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1807,24 +1807,28 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2019NE00547</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>2019NE00531</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>981.58</v>
+        <v>5440</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1833,14 +1837,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00073 e 2019GR00075</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2019NE00561</t>
+          <t>2019NE00484</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1850,7 +1854,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>916.14</v>
+        <v>121.02</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1859,14 +1863,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2019NE00559</t>
+          <t>2019NE00555</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1876,7 +1880,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5077.33</v>
+        <v>1815.33</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1885,28 +1889,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00043 e 2019GR00044.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2019NE00532</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00478</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5440</v>
+        <v>981.58</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1915,14 +1915,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO.2019GR00066 e 2019GR00120.</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2019NE00558</t>
+          <t>2019NE00489</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>981.58</v>
+        <v>5440</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1941,14 +1941,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO.</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2019NE00545</t>
+          <t>2019NE00496</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1967,14 +1967,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão. 2019GR00096 e 2019GR00109.</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2019NE00493</t>
+          <t>2019NE00468</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5440</v>
+        <v>1815.33</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2019NE00541</t>
+          <t>2019NE00494</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2019,14 +2019,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão. 2019GR00096 e 2019GR00109.</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2019NE00546</t>
+          <t>2019NE00487</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2780</v>
+        <v>185.33</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2045,24 +2045,28 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão. 2019GR00111 e 2019GR00121.</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2019NE00543</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>2019NE00538</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>981.58</v>
+        <v>1815.33</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2071,17 +2075,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO 541 EQUIVOCO NA MODALIDADE DE LICITAÇÃO</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00093 e 2019GR00094.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2019NE00554</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>2019NE00537</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
           <t>26/12/2019</t>
@@ -2097,24 +2105,28 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00069 e 2019GR00070</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão. 2019GR00060 e 2019GR00086.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2019NE00542</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>2019NE00536</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2780</v>
+        <v>1815.33</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2123,17 +2135,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão. 2019GR00111 e 2019GR00121.</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão. 2019GR00052 e 2019GR00053</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2019NE00477</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>2019NE00539</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
           <t>26/12/2019</t>
@@ -2149,24 +2165,28 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão. 2019GR00107 e 2019GR00108.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2019NE00474</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>2019NE00535</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2780</v>
+        <v>5440</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2175,14 +2195,14 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão. 2019GR00055 e 2019GR00056</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2019NE00475</t>
+          <t>2019NE00483</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2192,7 +2212,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1815.33</v>
+        <v>916.14</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2208,7 +2228,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2019NE00483</t>
+          <t>2019NE00475</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2218,7 +2238,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>916.14</v>
+        <v>1815.33</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2234,21 +2254,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2019NE00535</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00474</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5440</v>
+        <v>2780</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2257,21 +2273,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão. 2019GR00055 e 2019GR00056</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2019NE00539</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00477</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>26/12/2019</t>
@@ -2287,28 +2299,24 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão. 2019GR00107 e 2019GR00108.</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2019NE00536</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00542</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1815.33</v>
+        <v>2780</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2317,21 +2325,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão. 2019GR00052 e 2019GR00053</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão. 2019GR00111 e 2019GR00121.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2019NE00537</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00554</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>26/12/2019</t>
@@ -2347,28 +2351,24 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão. 2019GR00060 e 2019GR00086.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00069 e 2019GR00070</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2019NE00538</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00543</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1815.33</v>
+        <v>981.58</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2377,14 +2377,14 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00093 e 2019GR00094.</t>
+          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO 541 EQUIVOCO NA MODALIDADE DE LICITAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2019NE00487</t>
+          <t>2019NE00546</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>185.33</v>
+        <v>2780</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2403,14 +2403,14 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão. 2019GR00111 e 2019GR00121.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2019NE00494</t>
+          <t>2019NE00541</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão. 2019GR00096 e 2019GR00109.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2019NE00468</t>
+          <t>2019NE00493</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1815.33</v>
+        <v>5440</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2019NE00496</t>
+          <t>2019NE00545</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2481,14 +2481,14 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão. 2019GR00096 e 2019GR00109.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2019NE00489</t>
+          <t>2019NE00558</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5440</v>
+        <v>981.58</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2507,24 +2507,28 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2019NE00478</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>2019NE00532</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>981.58</v>
+        <v>5440</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2533,14 +2537,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO.2019GR00066 e 2019GR00120.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2019NE00555</t>
+          <t>2019NE00559</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2550,7 +2554,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1815.33</v>
+        <v>5077.33</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2559,14 +2563,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00043 e 2019GR00044.</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2019NE00484</t>
+          <t>2019NE00561</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2576,7 +2580,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>121.02</v>
+        <v>916.14</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2585,28 +2589,24 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2019NE00531</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00547</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5440</v>
+        <v>981.58</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2615,14 +2615,14 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00073 e 2019GR00075</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO, através do circuito de transmissão.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2019NE00562</t>
+          <t>2019NE00560</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>121.02</v>
+        <v>2594.67</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2641,28 +2641,24 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao.</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2019NE00540</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00564</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1815.33</v>
+        <v>362.67</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2671,14 +2667,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO.</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2019NE00485</t>
+          <t>2019NE00563</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2697,14 +2693,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2019NE00480</t>
+          <t>2019NE00568</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2714,7 +2710,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5077.33</v>
+        <v>1694.31</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2723,14 +2719,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão, Competência: Julho/18.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2019NE00565</t>
+          <t>2019NE00491</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2740,7 +2736,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>185.33</v>
+        <v>2780</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2749,14 +2745,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2019NE00469</t>
+          <t>2019NE00471</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2766,7 +2762,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2780</v>
+        <v>5440</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2782,7 +2778,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2019NE00530</t>
+          <t>2019NE00534</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2796,7 +2792,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1815.33</v>
+        <v>981.58</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2805,24 +2801,28 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00051 E 2019GR00071</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dados de transmissão. 2019GR00082 e 2019GR00083.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2019NE00556</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>2019NE00533</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
           <t>26/12/2019</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2780</v>
+        <v>981.58</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2831,14 +2831,14 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00045 e 2019GR00063.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00048, 2019GR00049</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2019NE00544</t>
+          <t>2019NE00482</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2780</v>
+        <v>2594.67</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2857,14 +2857,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NOTA DE EMPENHO 542 EQUIVOCO NA MODALIDADE DE LICITAÇÃO</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2019NE00470</t>
+          <t>2019NE00495</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5440</v>
+        <v>2780</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2019NE00479</t>
+          <t>2019NE00481</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>165.78</v>
+        <v>1694.31</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2019NE00472</t>
+          <t>2019NE00473</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>981.58</v>
+        <v>1815.33</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2019NE00557</t>
+          <t>2019NE00486</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5440</v>
+        <v>362.67</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2961,14 +2961,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO. 2019GR00046 e 2019GR00064</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2019NE00567</t>
+          <t>2019NE00488</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2780</v>
+        <v>981.58</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2987,14 +2987,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o acesso a MetroMAO.</t>
+          <t>ANULAÇÃO DE EMPENHO EM CUMPRIMENTO A LEI DELEGADA Nº 122 DE 15/10/2019.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2019NE00516</t>
+          <t>2019NE00492</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3401.58</v>
+        <v>1815.33</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2019NE00476</t>
+          <t>2019NE00490</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2780</v>
+        <v>1815.33</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3076,14 +3076,10 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2017NE00055</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+          <t>2017NE00057</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
           <t>24/02/2017</t>
@@ -3099,7 +3095,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE CESSÃO DE DIREITO DE USO DE PROGRAMAS DE COMPUTAÇÃO PARA ATENDER AS DISPOSIÇÕES DO SISTEMA DE PROTOCOLO ELETRÔNICO EM PLATAFORMA WEB - SPROWEB</t>
+          <t>ANULAÇÃO DA NE N.055/2017 MOTIVO MODALIDADE INCORRETA</t>
         </is>
       </c>
     </row>
@@ -3136,10 +3132,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2017NE00057</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>2017NE00055</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
           <t>24/02/2017</t>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE N.055/2017 MOTIVO MODALIDADE INCORRETA</t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE CESSÃO DE DIREITO DE USO DE PROGRAMAS DE COMPUTAÇÃO PARA ATENDER AS DISPOSIÇÕES DO SISTEMA DE PROTOCOLO ELETRÔNICO EM PLATAFORMA WEB - SPROWEB</t>
         </is>
       </c>
     </row>
@@ -3304,14 +3304,10 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2018NE00244</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+          <t>2018NE00228</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
           <t>21/06/2018</t>
@@ -3327,17 +3323,21 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>4º termo aditivo ao Contrato nº 004/2014 - Prorrogação de Contrato.</t>
+          <t>anulação desta NE00215/2018</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2018NE00228</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>2018NE00244</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
           <t>21/06/2018</t>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>anulação desta NE00215/2018</t>
+          <t>4º termo aditivo ao Contrato nº 004/2014 - Prorrogação de Contrato.</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2016NE00112</t>
+          <t>2016NE00111</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3882.75</v>
+        <v>750</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3503,14 +3503,14 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>REF: A CONTRATAÇÃO DOS SERVIÇOS DE CESSÃO DE DIREITO DE USO DE PROGRAMAS DE COMPUTAÇÃO PARA A DISPOSIÇÃO DO SISTEMA DE PROTOCOLO ELETRONICO EM PLATAFORMA WEB - SPROWEB.</t>
+          <t>OBJETO: PRESTAÇÃO DE SERVIÇOS DE CESSÃO DE DIREITO DE USO DE PROGRAMA ESPECIALIZADO EM PLATAFORME DE TRAMITES ELETRONICO - SPROWEB, MES: 12/2015.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2016NE00111</t>
+          <t>2016NE00112</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>750</v>
+        <v>3882.75</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>OBJETO: PRESTAÇÃO DE SERVIÇOS DE CESSÃO DE DIREITO DE USO DE PROGRAMA ESPECIALIZADO EM PLATAFORME DE TRAMITES ELETRONICO - SPROWEB, MES: 12/2015.</t>
+          <t>REF: A CONTRATAÇÃO DOS SERVIÇOS DE CESSÃO DE DIREITO DE USO DE PROGRAMAS DE COMPUTAÇÃO PARA A DISPOSIÇÃO DO SISTEMA DE PROTOCOLO ELETRONICO EM PLATAFORMA WEB - SPROWEB.</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2018NE00101</t>
+          <t>2018NE00097</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1689.62</v>
+        <v>66101.46000000001</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3593,19 +3593,19 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Contratacao dos servicos de cessao de direito de uso do programa de computacao para atender as disposicoes do sistema de protocolo eletronico em plataforma web sproweb</t>
+          <t>Prestação de serviços de Rede, compreendendo o acesso à Metromao, através de circuito de transmissão de dados interligados - link</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2018NE00097</t>
+          <t>2018NE00101</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>66101.46000000001</v>
+        <v>1689.62</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Prestação de serviços de Rede, compreendendo o acesso à Metromao, através de circuito de transmissão de dados interligados - link</t>
+          <t>Contratacao dos servicos de cessao de direito de uso do programa de computacao para atender as disposicoes do sistema de protocolo eletronico em plataforma web sproweb</t>
         </is>
       </c>
     </row>
@@ -3660,12 +3660,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2018NE00215</t>
+          <t>2018NE00214</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10137.72</v>
+        <v>66101.46000000001</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3683,19 +3683,19 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Referente ao 4º Termo Aditivo ao Termo de Contrato nº 004/2014,Prorrogar Prazo de Vigência por mais 12 meses 28/02/2018 27/02/2018</t>
+          <t>REFERENTE AO TERMO DE CONTRATO Nº 003/2017 DOS SERVIÇOS DE FIREWALL,ACESSO A METROMAO,FORNECIMENTO DE TRANSMISSÃO DE DADOS E ACESSO A REDE MUNDIAL NOS MESES DE JANEIRO A JUNHO/2018</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2018NE00214</t>
+          <t>2018NE00215</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>66101.46000000001</v>
+        <v>10137.72</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>REFERENTE AO TERMO DE CONTRATO Nº 003/2017 DOS SERVIÇOS DE FIREWALL,ACESSO A METROMAO,FORNECIMENTO DE TRANSMISSÃO DE DADOS E ACESSO A REDE MUNDIAL NOS MESES DE JANEIRO A JUNHO/2018</t>
+          <t>Referente ao 4º Termo Aditivo ao Termo de Contrato nº 004/2014,Prorrogar Prazo de Vigência por mais 12 meses 28/02/2018 27/02/2018</t>
         </is>
       </c>
     </row>
@@ -3750,21 +3750,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2016NE00100</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+          <t>2016NE00109</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
           <t>04/03/2016</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>776.55</v>
+        <v>750</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3773,17 +3769,21 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO SERVIÇO DE FORNECIMENTO DE CESSÃO DE DIREITO DE USO DE PROGRAMAS DE COMPUTAÇÃO PARA A DISPOSIÇÃO DO SISTEMA DE PROTOCOLO ELETRONICO EM PLATAFORMA WEB - SPROWEB.</t>
+          <t>REF. AO ERRO NA NATUREZA.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2016NE00107</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>2016NE00108</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
           <t>04/03/2016</t>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>REF: AO ERRO NA ORIGEM DO MATERIAL.</t>
+          <t>REF: PRESTAÇÃO DE SERVIÇOS DE CESSÃO DE DIREITO DE USO DE PROGRAMA ESPECIALIZADO EM PLATAFORME DE TRAMITES ELETRONICO - SPROWEB, MES: 12/2015.</t>
         </is>
       </c>
     </row>
@@ -3836,14 +3836,10 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2016NE00108</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+          <t>2016NE00107</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
           <t>04/03/2016</t>
@@ -3859,24 +3855,28 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>REF: PRESTAÇÃO DE SERVIÇOS DE CESSÃO DE DIREITO DE USO DE PROGRAMA ESPECIALIZADO EM PLATAFORME DE TRAMITES ELETRONICO - SPROWEB, MES: 12/2015.</t>
+          <t>REF: AO ERRO NA ORIGEM DO MATERIAL.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2016NE00109</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>2016NE00100</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
           <t>04/03/2016</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>750</v>
+        <v>776.55</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>REF. AO ERRO NA NATUREZA.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO SERVIÇO DE FORNECIMENTO DE CESSÃO DE DIREITO DE USO DE PROGRAMAS DE COMPUTAÇÃO PARA A DISPOSIÇÃO DO SISTEMA DE PROTOCOLO ELETRONICO EM PLATAFORMA WEB - SPROWEB.</t>
         </is>
       </c>
     </row>
@@ -3974,21 +3974,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2019NE00008</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00028</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>33050.73</v>
+        <v>2112.02</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -3997,28 +3993,24 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE INFORMATICA, REDE COMPREENDENDO O ACESSO A METROMAO ATRAVES DO CIRCUITO DE TRANSMISSÃO DE DADOS.</t>
+          <t>anulação para correção da descrição</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2019NE00001</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+          <t>2019NE00037</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2112.02</v>
+        <v>33050.73</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4027,19 +4019,19 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada do Serviço de Disponibilização de Sistema de Protocolo em plataforma WEB, com acréscimo de 25%, devido a inclusão de itens de faturamento para nova versão do SPROW</t>
+          <t>ANULAÇÃO DESTA NE, MOTIVO DESCRIÇÃO INCORRETA.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2019NE00032</t>
+          <t>2019NE00050</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4048,7 +4040,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2112.02</v>
+        <v>33050.73</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4057,19 +4049,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada do Serviço de Disponibilização de Sistema de Protocolo em plataforma WEB, com acréscimo de 25%, devido a inclusão de itens de faturamento para nova versão do SPROW</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE INFORMATICA, REDE COMPREENDENDO O ACESSO A METROMAO ATRAVES DO CIRCUITO DE TRANSMISSÃO DE DADOS.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2019NE00050</t>
+          <t>2019NE00032</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4078,7 +4070,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>33050.73</v>
+        <v>2112.02</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4087,24 +4079,28 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE INFORMATICA, REDE COMPREENDENDO O ACESSO A METROMAO ATRAVES DO CIRCUITO DE TRANSMISSÃO DE DADOS.</t>
+          <t>Contratação de Empresa Especializada do Serviço de Disponibilização de Sistema de Protocolo em plataforma WEB, com acréscimo de 25%, devido a inclusão de itens de faturamento para nova versão do SPROW</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2019NE00037</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>2019NE00001</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>33050.73</v>
+        <v>2112.02</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4113,24 +4109,28 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DESTA NE, MOTIVO DESCRIÇÃO INCORRETA.</t>
+          <t>Contratação de Empresa Especializada do Serviço de Disponibilização de Sistema de Protocolo em plataforma WEB, com acréscimo de 25%, devido a inclusão de itens de faturamento para nova versão do SPROW</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2019NE00028</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>2019NE00008</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2112.02</v>
+        <v>33050.73</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>anulação para correção da descrição</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE INFORMATICA, REDE COMPREENDENDO O ACESSO A METROMAO ATRAVES DO CIRCUITO DE TRANSMISSÃO DE DADOS.</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4176,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2014NE00036</t>
+          <t>2014NE00022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>10/2013</t>
+          <t>2/2014</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>177543.36</v>
+        <v>169021.44</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Contrato No. 10/2013 - 8 links ponto a ponto e Internet 3Mbps via MetroMAO</t>
+          <t>Contrato N. 002/2014 - Serviços Técnico de Rede, Link, MetroMAO</t>
         </is>
       </c>
     </row>
@@ -4236,12 +4236,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2014NE00022</t>
+          <t>2014NE00036</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2/2014</t>
+          <t>10/2013</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>169021.44</v>
+        <v>177543.36</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4259,19 +4259,19 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Contrato N. 002/2014 - Serviços Técnico de Rede, Link, MetroMAO</t>
+          <t>Contrato No. 10/2013 - 8 links ponto a ponto e Internet 3Mbps via MetroMAO</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2017NE00373</t>
+          <t>2017NE00367</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1689.62</v>
+        <v>22033.82</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4289,19 +4289,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Empenho será destinado a cobrir despesas com o contrato n. 004/2014 - SETRAB, referente a prestação de serviços de disponibilidade do Sistema SPRWEB, mês de referência Novembro e Dezembro.</t>
+          <t>Prestação de serviços de Rede, compreendendo o acesso à Metromao, através de circuito de transmissão de dados interligados - link - meses de outubro e novembro.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2017NE00367</t>
+          <t>2017NE00373</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>22033.82</v>
+        <v>1689.62</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4319,28 +4319,24 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Prestação de serviços de Rede, compreendendo o acesso à Metromao, através de circuito de transmissão de dados interligados - link - meses de outubro e novembro.</t>
+          <t>Empenho será destinado a cobrir despesas com o contrato n. 004/2014 - SETRAB, referente a prestação de serviços de disponibilidade do Sistema SPRWEB, mês de referência Novembro e Dezembro.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2016NE00581</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+          <t>2016NE00572</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>776.55</v>
+        <v>193.3</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4349,24 +4345,28 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO SERVIÇO DE FORNECIMENTO DE CESSÃO DE DIREITO DE USO DE PROGRAMAS DE COMPUTAÇÃO PARA A DISPOSIÇÃO DO SISTEMA DE PROTOCOLO ELETRONICO EM PLATAFORMA WEB - </t>
+          <t>reserva</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2016NE00572</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>2016NE00581</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>193.3</v>
+        <v>776.55</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>reserva</t>
+          <t xml:space="preserve">OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO SERVIÇO DE FORNECIMENTO DE CESSÃO DE DIREITO DE USO DE PROGRAMAS DE COMPUTAÇÃO PARA A DISPOSIÇÃO DO SISTEMA DE PROTOCOLO ELETRONICO EM PLATAFORMA WEB - </t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,11 @@
           <t>2016NE00512</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>4/2014</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
           <t>01/11/2016</t>
@@ -4463,11 +4467,7 @@
           <t>2016NE00512</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>4/2014</t>
-        </is>
-      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
           <t>01/11/2016</t>
@@ -4490,10 +4490,14 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2018NE00506</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>2018NE00491</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
           <t>01/10/2018</t>
@@ -4509,21 +4513,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ANULAÇÃO QUE SE FAZ PARA CORREÇÃO DO SUBITEM DA NATUREZA DE DESPESAS.</t>
+          <t>Prestação do serviço de Rede, compreendendo o acesso a MetroMAO, através do circuito de transmissão de Dados para atender a SETRAB, 1º TACT 003/2017 - prorrogação prazo de vigência por mais 12 meses.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2018NE00491</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2018NE00506</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
           <t>01/10/2018</t>
@@ -4539,14 +4539,14 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Prestação do serviço de Rede, compreendendo o acesso a MetroMAO, através do circuito de transmissão de Dados para atender a SETRAB, 1º TACT 003/2017 - prorrogação prazo de vigência por mais 12 meses.</t>
+          <t>ANULAÇÃO QUE SE FAZ PARA CORREÇÃO DO SUBITEM DA NATUREZA DE DESPESAS.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2016NE00475</t>
+          <t>2016NE00465</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1553.1</v>
+        <v>776.55</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4569,14 +4569,14 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>RESERVA</t>
+          <t>100171 - SERVIÇOS DE LICENÇAS DE SOFTWARES, Descrição: SERVIÇOS DE LICENÇAS DE SOFTWARES, Descrição: Licença de uso de Sistema de Protocolo em plataforma WEB, conforme Projeto Básico MARCA: null REFER</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2016NE00475</t>
+          <t>2016NE00465</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1553.1</v>
+        <v>776.55</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4595,14 +4595,14 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>RESERVA</t>
+          <t>100171 - SERVIÇOS DE LICENÇAS DE SOFTWARES, Descrição: SERVIÇOS DE LICENÇAS DE SOFTWARES, Descrição: Licença de uso de Sistema de Protocolo em plataforma WEB, conforme Projeto Básico MARCA: null REFER</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2016NE00465</t>
+          <t>2016NE00475</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>776.55</v>
+        <v>1553.1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4621,14 +4621,14 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>100171 - SERVIÇOS DE LICENÇAS DE SOFTWARES, Descrição: SERVIÇOS DE LICENÇAS DE SOFTWARES, Descrição: Licença de uso de Sistema de Protocolo em plataforma WEB, conforme Projeto Básico MARCA: null REFER</t>
+          <t>RESERVA</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2016NE00465</t>
+          <t>2016NE00475</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>776.55</v>
+        <v>1553.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>100171 - SERVIÇOS DE LICENÇAS DE SOFTWARES, Descrição: SERVIÇOS DE LICENÇAS DE SOFTWARES, Descrição: Licença de uso de Sistema de Protocolo em plataforma WEB, conforme Projeto Básico MARCA: null REFER</t>
+          <t>RESERVA</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2019NE00287</t>
+          <t>2019NE00289</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>418.38</v>
+        <v>282.54</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4819,19 +4819,19 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Anulação que se faz de saldo de empenho de Contrato não executado despesa na sua totalidade mensalmente.</t>
+          <t>Anulação que se faz de saldo de empenho de Contrato não executado despesa no valor mensal previsto.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2019NE00312</t>
+          <t>2019NE00313</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>2/2019</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>10965.75</v>
+        <v>2260.9</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -4849,19 +4849,19 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos Serviços de Informática, Rede compreendendo o acesso a Metromao através co circuito de transmissão de dados.</t>
+          <t>Reforco que se faz do cronograma de julho e agosto do Termo de Contrato nº 002/2019 que tem como objeto a prestação de serviços de Uso de Sistema de Protocolo em plataforma Web (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2019NE00313</t>
+          <t>2019NE00312</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2/2019</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2260.9</v>
+        <v>10965.75</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -4879,14 +4879,14 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Reforco que se faz do cronograma de julho e agosto do Termo de Contrato nº 002/2019 que tem como objeto a prestação de serviços de Uso de Sistema de Protocolo em plataforma Web (SPROWEB).</t>
+          <t>Contratação de empresa especializada na prestação dos Serviços de Informática, Rede compreendendo o acesso a Metromao através co circuito de transmissão de dados.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2019NE00289</t>
+          <t>2019NE00287</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>282.54</v>
+        <v>418.38</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Anulação que se faz de saldo de empenho de Contrato não executado despesa no valor mensal previsto.</t>
+          <t>Anulação que se faz de saldo de empenho de Contrato não executado despesa na sua totalidade mensalmente.</t>
         </is>
       </c>
     </row>
@@ -4994,21 +4994,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2019NE00129</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00138</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
           <t>01/04/2019</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2780</v>
+        <v>33050.73</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5017,14 +5013,14 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE INFORMATICA, REDE COMPREENDENDO O ACESSO A METROMAO ATRAVES DO CIRCUITO DE TRANSMISSÃO DE DADOS.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2019NE00117</t>
+          <t>2019NE00125</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5038,7 +5034,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5077.33</v>
+        <v>185.33</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5054,17 +5050,21 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2019NE00134</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
+          <t>2019NE00119</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C161" t="inlineStr">
         <is>
           <t>01/04/2019</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>981.58</v>
+        <v>2594.67</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5073,14 +5073,14 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Anulação da Nota de Empenho nº. 104 - equivoco no elemento de despesas</t>
+          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2019NE00130</t>
+          <t>2019NE00122</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1815.33</v>
+        <v>121.02</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5103,14 +5103,14 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>1.º (Primeiro) Termo Aditivo ao Contrato n.º 003/2017-SETRAB. Prorrogação do Prazo Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o aces</t>
+          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2019NE00133</t>
+          <t>2019NE00128</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2780</v>
+        <v>1815.33</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5133,14 +5133,14 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>1.º (Primeiro) Termo Aditivo ao Contrato n.º 003/2017-SETRAB. Prorrogação do Prazo Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o aces</t>
+          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2019NE00132</t>
+          <t>2019NE00126</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5163,14 +5163,14 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>1.º (Primeiro) Termo Aditivo ao Contrato n.º 003/2017-SETRAB. Prorrogação do Prazo Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o aces</t>
+          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2019NE00124</t>
+          <t>2019NE00131</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>362.67</v>
+        <v>5440</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5193,19 +5193,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
+          <t>1.º (Primeiro) Termo Aditivo ao Contrato n.º 003/2017-SETRAB. Prorrogação do Prazo Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o aces</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2019NE00121</t>
+          <t>2019NE00116</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3/2017</t>
+          <t>2/2019</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5214,7 +5214,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>916.14</v>
+        <v>3391.35</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5223,14 +5223,14 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de execução de Sistema de Protocolo em plataforma web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os document</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2019NE00127</t>
+          <t>2019NE00118</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>5440</v>
+        <v>1694.31</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2019NE00118</t>
+          <t>2019NE00127</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1694.31</v>
+        <v>5440</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5320,12 +5320,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2019NE00116</t>
+          <t>2019NE00121</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2/2019</t>
+          <t>3/2017</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3391.35</v>
+        <v>916.14</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5343,14 +5343,14 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de execução de Sistema de Protocolo em plataforma web (SPROWEB), objetivando o controle e acompanhamento do registro de todos os document</t>
+          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2019NE00131</t>
+          <t>2019NE00124</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>5440</v>
+        <v>362.67</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5373,14 +5373,14 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1.º (Primeiro) Termo Aditivo ao Contrato n.º 003/2017-SETRAB. Prorrogação do Prazo Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o aces</t>
+          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2019NE00126</t>
+          <t>2019NE00132</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5403,14 +5403,14 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
+          <t>1.º (Primeiro) Termo Aditivo ao Contrato n.º 003/2017-SETRAB. Prorrogação do Prazo Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o aces</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2019NE00128</t>
+          <t>2019NE00133</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5424,7 +5424,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1815.33</v>
+        <v>2780</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5433,14 +5433,14 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
+          <t>1.º (Primeiro) Termo Aditivo ao Contrato n.º 003/2017-SETRAB. Prorrogação do Prazo Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o aces</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2019NE00122</t>
+          <t>2019NE00130</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>121.02</v>
+        <v>1815.33</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5463,28 +5463,24 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
+          <t>1.º (Primeiro) Termo Aditivo ao Contrato n.º 003/2017-SETRAB. Prorrogação do Prazo Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Acesso a Rede Mundial, compreendendo o aces</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2019NE00119</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>3/2017</t>
-        </is>
-      </c>
+          <t>2019NE00134</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
           <t>01/04/2019</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2594.67</v>
+        <v>981.58</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5493,14 +5489,14 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
+          <t>Anulação da Nota de Empenho nº. 104 - equivoco no elemento de despesas</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2019NE00125</t>
+          <t>2019NE00117</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5514,7 +5510,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>185.33</v>
+        <v>5077.33</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5530,17 +5526,21 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2019NE00138</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr"/>
+          <t>2019NE00129</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>3/2017</t>
+        </is>
+      </c>
       <c r="C177" t="inlineStr">
         <is>
           <t>01/04/2019</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>33050.73</v>
+        <v>2780</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM PRESTAÇÃO DE SERVIÇOS DE INFORMATICA, REDE COMPREENDENDO O ACESSO A METROMAO ATRAVES DO CIRCUITO DE TRANSMISSÃO DE DADOS.</t>
+          <t>1º Termo Aditivo ao Contrato nº 003/2017. Objeto: Contratação de empresa especializada na prestação dos serviços de Acesso a Rede Mundial, compreendendo o acesso a Metromao, através de circuito de dad</t>
         </is>
       </c>
     </row>
